--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -380,7 +380,7 @@
 </t>
   </si>
   <si>
-    <t>Persistenter Identifikator für das Bundle.</t>
+    <t>Persistent identifier for the bundle</t>
   </si>
   <si>
     <t>A persistent identifier for the bundle that won't change as a bundle is copied from server to server.</t>
@@ -478,7 +478,7 @@
 </t>
   </si>
   <si>
-    <t>Verweise auf weiterführende Informationen zum Bundle.</t>
+    <t>Links related to this Bundle</t>
   </si>
   <si>
     <t>A series of links that provide context to this bundle.</t>
@@ -605,7 +605,7 @@
     <t>Bundle.entry.link</t>
   </si>
   <si>
-    <t>Verweise auf weiterführende Informationen zu diesem Entry.</t>
+    <t>Links related to this entry</t>
   </si>
   <si>
     <t>A series of links that provide context to this entry.</t>
@@ -614,7 +614,7 @@
     <t>Bundle.entry.fullUrl</t>
   </si>
   <si>
-    <t xml:space="preserve">Eindeutige URL für den Eintrag im Bundle. </t>
+    <t>URI for resource (Absolute URL server address or URI for UUID/OID)</t>
   </si>
   <si>
     <t>The Absolute URL for the resource.  The fullUrl SHALL NOT disagree with the id in the resource - i.e. if the fullUrl is not a urn:uuid, the URL shall be version-independent URL consistent with the Resource.id. The fullUrl is a version independent reference to the resource. The fullUrl element SHALL have a value except that: 
@@ -2160,7 +2160,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2176,10 +2176,10 @@
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
@@ -2632,7 +2632,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -3315,7 +3315,7 @@
         <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan (Aktualisierung aller enthaltenen Ressourcen) und besteht aus: 
+    <t>Das Medikationsplan-Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den Medikationsplan (Aktualisierung aller enthaltenen Ressourcen) und enthält: 
 - 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus 
 - 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung
 Alle neuen bzw. geänderten und zu entfernenden Medikationsplaneinträge müssen inline im Bundle enthalten sein, alle unveränderten Ressourcen werden referenziert.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2388,7 +2388,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -2401,13 +2401,13 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2486,7 +2486,7 @@
     <t>Bundle.entry.resource.emptyReason</t>
   </si>
   <si>
-    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown | unavailable] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Patient nimmt derzeit keine Medikamente ein | unavailable: Plan ist leer weil alle Einträge entfernt wurden</t>
+    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown ] Bedeutung: notstarted: Intitalzustand - noch nie befüllt; nilknown: Der Plan wurde vom GDA explizit als leer dokumentiert oder alle Einträge wurden abgesetzt, storniert oder gelöscht.</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -429,7 +429,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitpunkt der Erstellung des Bundles.</t>
+    <t>When the bundle was assembled</t>
   </si>
   <si>
     <t>The date/time that the bundle was assembled - i.e. when the resources were placed in the bundle.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8278" uniqueCount="896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8278" uniqueCount="894">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1626,7 +1626,7 @@
     <t>Bundle.entry.resource.code.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
+    <t>Fachliche Begründung: TODO</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -1779,9 +1779,6 @@
     <t>Bundle.entry.resource.subject.identifier.use</t>
   </si>
   <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
     <t>The purpose of this identifier.</t>
   </si>
   <si>
@@ -2140,9 +2137,6 @@
   </si>
   <si>
     <t>Bundle.entry.resource.orderedBy</t>
-  </si>
-  <si>
-    <t>Fachliche Begründung: TODO</t>
   </si>
   <si>
     <t>What order applies to the items in the list.</t>
@@ -13947,7 +13941,7 @@
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>21</v>
@@ -14973,7 +14967,7 @@
         <v>78</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>21</v>
@@ -14988,16 +14982,16 @@
         <v>107</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>21</v>
@@ -15025,28 +15019,28 @@
         <v>127</v>
       </c>
       <c r="Y105" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="Z105" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="Z105" t="s" s="2">
+      <c r="AA105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF105" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15064,7 +15058,7 @@
         <v>84</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>21</v>
@@ -15075,10 +15069,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15104,16 +15098,16 @@
         <v>444</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="N106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>21</v>
@@ -15141,28 +15135,28 @@
         <v>321</v>
       </c>
       <c r="Y106" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="Z106" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="Z106" t="s" s="2">
+      <c r="AA106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15177,10 +15171,10 @@
         <v>99</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>21</v>
@@ -15191,10 +15185,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15220,16 +15214,16 @@
         <v>101</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
@@ -15242,43 +15236,43 @@
         <v>21</v>
       </c>
       <c r="T107" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF107" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15293,10 +15287,10 @@
         <v>99</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AL107" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>21</v>
@@ -15307,10 +15301,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15336,13 +15330,13 @@
         <v>150</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15356,43 +15350,43 @@
         <v>21</v>
       </c>
       <c r="T108" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF108" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15407,10 +15401,10 @@
         <v>99</v>
       </c>
       <c r="AK108" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AL108" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>21</v>
@@ -15421,10 +15415,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15447,13 +15441,13 @@
         <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15504,7 +15498,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15519,10 +15513,10 @@
         <v>99</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AL109" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>21</v>
@@ -15533,10 +15527,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15559,16 +15553,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15618,7 +15612,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15633,10 +15627,10 @@
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AL110" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>21</v>
@@ -15647,10 +15641,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15676,13 +15670,13 @@
         <v>150</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15732,7 +15726,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15761,10 +15755,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15787,13 +15781,13 @@
         <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="M112" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15844,7 +15838,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15862,21 +15856,21 @@
         <v>21</v>
       </c>
       <c r="AL112" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN112" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>633</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15899,19 +15893,19 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="N113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
@@ -15960,7 +15954,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15978,25 +15972,25 @@
         <v>21</v>
       </c>
       <c r="AL113" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>643</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -16015,19 +16009,19 @@
         <v>88</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>21</v>
@@ -16076,7 +16070,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16094,21 +16088,21 @@
         <v>21</v>
       </c>
       <c r="AL114" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>654</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16217,10 +16211,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B116" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16331,10 +16325,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B117" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16445,10 +16439,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="B118" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16559,10 +16553,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B119" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16673,10 +16667,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="B120" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16785,10 +16779,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B121" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16899,10 +16893,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="B122" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16913,7 +16907,7 @@
         <v>78</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>21</v>
@@ -16928,16 +16922,16 @@
         <v>107</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="N122" t="s" s="2">
+      <c r="O122" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>21</v>
@@ -16965,28 +16959,28 @@
         <v>127</v>
       </c>
       <c r="Y122" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="Z122" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="Z122" t="s" s="2">
+      <c r="AA122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF122" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -17004,7 +16998,7 @@
         <v>84</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>21</v>
@@ -17015,10 +17009,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17044,16 +17038,16 @@
         <v>444</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>21</v>
@@ -17081,28 +17075,28 @@
         <v>321</v>
       </c>
       <c r="Y123" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="Z123" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="Z123" t="s" s="2">
+      <c r="AA123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF123" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17117,10 +17111,10 @@
         <v>99</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>21</v>
@@ -17131,10 +17125,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17160,16 +17154,16 @@
         <v>101</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="N124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>21</v>
@@ -17182,43 +17176,43 @@
         <v>21</v>
       </c>
       <c r="T124" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF124" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17233,10 +17227,10 @@
         <v>99</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AL124" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>21</v>
@@ -17247,10 +17241,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17276,13 +17270,13 @@
         <v>150</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17296,43 +17290,43 @@
         <v>21</v>
       </c>
       <c r="T125" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF125" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17347,10 +17341,10 @@
         <v>99</v>
       </c>
       <c r="AK125" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AL125" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>21</v>
@@ -17361,10 +17355,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17387,13 +17381,13 @@
         <v>88</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L126" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="M126" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17444,7 +17438,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -17459,10 +17453,10 @@
         <v>99</v>
       </c>
       <c r="AK126" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AL126" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>21</v>
@@ -17473,10 +17467,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="B127" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17499,16 +17493,16 @@
         <v>88</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="L127" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="L127" t="s" s="2">
+      <c r="M127" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17558,7 +17552,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17573,10 +17567,10 @@
         <v>99</v>
       </c>
       <c r="AK127" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AL127" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>21</v>
@@ -17587,10 +17581,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17616,13 +17610,13 @@
         <v>150</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17672,7 +17666,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17701,10 +17695,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17730,16 +17724,16 @@
         <v>444</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="N129" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>21</v>
@@ -17767,28 +17761,28 @@
         <v>111</v>
       </c>
       <c r="Y129" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF129" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17806,7 +17800,7 @@
         <v>21</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>21</v>
@@ -17817,10 +17811,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17843,13 +17837,13 @@
         <v>21</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17900,7 +17894,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17918,7 +17912,7 @@
         <v>21</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>21</v>
@@ -17929,10 +17923,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17958,13 +17952,13 @@
         <v>145</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18014,7 +18008,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -18023,7 +18017,7 @@
         <v>79</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>99</v>
@@ -18032,7 +18026,7 @@
         <v>21</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>21</v>
@@ -18043,10 +18037,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18155,10 +18149,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18269,10 +18263,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18385,10 +18379,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18414,16 +18408,16 @@
         <v>444</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="N135" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>21</v>
@@ -18452,7 +18446,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>21</v>
@@ -18470,7 +18464,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18499,10 +18493,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18611,10 +18605,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18725,10 +18719,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18739,7 +18733,7 @@
         <v>87</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>88</v>
@@ -18841,10 +18835,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18953,10 +18947,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19067,10 +19061,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19183,10 +19177,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19297,10 +19291,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19411,10 +19405,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19525,10 +19519,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19641,10 +19635,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19655,7 +19649,7 @@
         <v>78</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>21</v>
@@ -19757,10 +19751,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19786,76 +19780,76 @@
         <v>398</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="N147" t="s" s="2">
         <v>746</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="O147" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="N147" t="s" s="2">
+      <c r="P147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q147" t="s" s="2">
         <v>748</v>
       </c>
-      <c r="O147" t="s" s="2">
+      <c r="R147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF147" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="P147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q147" t="s" s="2">
+      <c r="AG147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI147" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="R147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="AG147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH147" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI147" t="s" s="2">
-        <v>752</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>99</v>
@@ -19864,7 +19858,7 @@
         <v>21</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>21</v>
@@ -19875,10 +19869,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19901,17 +19895,17 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>21</v>
@@ -19960,7 +19954,7 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19978,7 +19972,7 @@
         <v>21</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>21</v>
@@ -19989,10 +19983,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20015,13 +20009,13 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="L149" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20072,7 +20066,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>87</v>
@@ -20090,7 +20084,7 @@
         <v>21</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>21</v>
@@ -20101,10 +20095,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20213,10 +20207,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20325,13 +20319,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B152" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="C152" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="C152" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>21</v>
@@ -20353,16 +20347,16 @@
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>774</v>
       </c>
-      <c r="L152" t="s" s="2">
+      <c r="N152" t="s" s="2">
         <v>775</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -20441,10 +20435,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20553,10 +20547,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20665,10 +20659,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20708,7 +20702,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>21</v>
@@ -20779,10 +20773,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20823,7 +20817,7 @@
         <v>21</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>21</v>
@@ -20891,10 +20885,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21005,10 +20999,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21119,10 +21113,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21233,10 +21227,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21262,13 +21256,13 @@
         <v>150</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="N160" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -21318,7 +21312,7 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -21347,10 +21341,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21376,16 +21370,16 @@
         <v>444</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="N161" t="s" s="2">
         <v>798</v>
       </c>
-      <c r="M161" t="s" s="2">
+      <c r="O161" t="s" s="2">
         <v>799</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>801</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>21</v>
@@ -21414,7 +21408,7 @@
       </c>
       <c r="Y161" s="2"/>
       <c r="Z161" t="s" s="2">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>21</v>
@@ -21432,7 +21426,7 @@
         <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -21441,7 +21435,7 @@
         <v>87</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>99</v>
@@ -21450,7 +21444,7 @@
         <v>21</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>21</v>
@@ -21461,10 +21455,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21573,10 +21567,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21687,10 +21681,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21701,7 +21695,7 @@
         <v>87</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>88</v>
@@ -21803,10 +21797,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21915,10 +21909,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22029,10 +22023,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22145,10 +22139,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22259,10 +22253,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22373,10 +22367,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22487,10 +22481,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22603,10 +22597,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22617,7 +22611,7 @@
         <v>78</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>21</v>
@@ -22719,7 +22713,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>195</v>
@@ -22831,7 +22825,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>199</v>
@@ -22943,7 +22937,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>200</v>
@@ -23057,7 +23051,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>201</v>
@@ -23173,7 +23167,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>202</v>
@@ -23287,7 +23281,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>208</v>
@@ -23401,7 +23395,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>213</v>
@@ -23513,7 +23507,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>217</v>
@@ -23625,7 +23619,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>218</v>
@@ -23739,7 +23733,7 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>219</v>
@@ -23855,7 +23849,7 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>220</v>
@@ -23967,7 +23961,7 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>225</v>
@@ -24081,7 +24075,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>229</v>
@@ -24193,7 +24187,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>232</v>
@@ -24305,7 +24299,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>234</v>
@@ -24417,7 +24411,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>237</v>
@@ -24529,7 +24523,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>240</v>
@@ -24641,7 +24635,7 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>244</v>
@@ -24753,7 +24747,7 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>245</v>
@@ -24867,7 +24861,7 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>246</v>
@@ -24983,7 +24977,7 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>247</v>
@@ -25095,7 +25089,7 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>250</v>
@@ -25207,7 +25201,7 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>253</v>
@@ -25321,7 +25315,7 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>257</v>
@@ -25435,7 +25429,7 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>261</v>
@@ -25549,13 +25543,13 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D198" t="s" s="2">
         <v>21</v>
@@ -25663,7 +25657,7 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>181</v>
@@ -25775,7 +25769,7 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>182</v>
@@ -25889,7 +25883,7 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>183</v>
@@ -26005,7 +25999,7 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>184</v>
@@ -26117,7 +26111,7 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>187</v>
@@ -26231,14 +26225,14 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
@@ -26257,13 +26251,13 @@
         <v>21</v>
       </c>
       <c r="K204" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="L204" t="s" s="2">
+        <v>860</v>
+      </c>
+      <c r="M204" t="s" s="2">
         <v>861</v>
-      </c>
-      <c r="L204" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="M204" t="s" s="2">
-        <v>863</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -26332,7 +26326,7 @@
         <v>21</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="AM204" t="s" s="2">
         <v>21</v>
@@ -26343,7 +26337,7 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>195</v>
@@ -26455,7 +26449,7 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>199</v>
@@ -26567,7 +26561,7 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>200</v>
@@ -26681,7 +26675,7 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>201</v>
@@ -26797,7 +26791,7 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>202</v>
@@ -26911,7 +26905,7 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>208</v>
@@ -27025,7 +27019,7 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>213</v>
@@ -27137,7 +27131,7 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>217</v>
@@ -27249,7 +27243,7 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>218</v>
@@ -27363,7 +27357,7 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>219</v>
@@ -27479,7 +27473,7 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>220</v>
@@ -27591,7 +27585,7 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>225</v>
@@ -27705,7 +27699,7 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>229</v>
@@ -27817,7 +27811,7 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>232</v>
@@ -27929,7 +27923,7 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>234</v>
@@ -28041,7 +28035,7 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>237</v>
@@ -28153,7 +28147,7 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>240</v>
@@ -28265,7 +28259,7 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>244</v>
@@ -28377,7 +28371,7 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>245</v>
@@ -28491,7 +28485,7 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>246</v>
@@ -28607,7 +28601,7 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>247</v>
@@ -28719,7 +28713,7 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>250</v>
@@ -28831,7 +28825,7 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>253</v>
@@ -28945,7 +28939,7 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>257</v>
@@ -29059,7 +29053,7 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>261</v>
@@ -29173,10 +29167,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -29199,19 +29193,19 @@
         <v>88</v>
       </c>
       <c r="K230" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="L230" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="M230" t="s" s="2">
         <v>891</v>
       </c>
-      <c r="L230" t="s" s="2">
+      <c r="N230" t="s" s="2">
         <v>892</v>
       </c>
-      <c r="M230" t="s" s="2">
+      <c r="O230" t="s" s="2">
         <v>893</v>
-      </c>
-      <c r="N230" t="s" s="2">
-        <v>894</v>
-      </c>
-      <c r="O230" t="s" s="2">
-        <v>895</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>21</v>
@@ -29260,7 +29254,7 @@
         <v>21</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>78</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,10 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Das Medikationsplan-Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den Medikationsplan (Aktualisierung aller enthaltenen Ressourcen) und enthält: 
-- 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus 
-- 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung
-Alle neuen bzw. geänderten und zu entfernenden Medikationsplaneinträge müssen inline im Bundle enthalten sein, alle unveränderten Ressourcen werden referenziert.</t>
+    <t>Profil für das Schreiben des Medikationsplans mit der $plan-write Operation.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -2170,7 +2167,7 @@
 </t>
   </si>
   <si>
-    <t>Fachliche Begrüundung: Auf dieser Ebene keine Freitext-Anmerkungen im Medikationsplan. Freitext ist in den jeweiligen MedicationRequests(Planeinträgen möglich)</t>
+    <t>Fachliche Begründung: Auf dieser Ebene keine Freitext-Anmerkungen im Medikationsplan. Freitext ist in den jeweiligen MedicationRequests(Planeinträgen möglich)</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8278" uniqueCount="894">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8271" uniqueCount="896">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -330,7 +330,7 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
+    <t>Fachliche Begründung: Die Ressource wird nach den Regeln dieses Implementierungsleitfadens interpretiert. Zusätzliche implizite Verarbeitungsregeln werden nicht verwendet.</t>
   </si>
   <si>
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
@@ -599,6 +599,12 @@
     <t>Bundle.entry.modifierExtension</t>
   </si>
   <si>
+    <t>Fachliche Begründung: Es sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
     <t>Bundle.entry.link</t>
   </si>
   <si>
@@ -1071,9 +1077,6 @@
     <t>Bundle.entry.resource.implicitRules</t>
   </si>
   <si>
-    <t>Fachliche Begründung: Die Ressource wird nach den Regeln dieses Implementierungsleitfadens interpretiert. Zusätzliche implizite Verarbeitungsregeln werden nicht verwendet.</t>
-  </si>
-  <si>
     <t>Bundle.entry:Medikationsplan.resource.language</t>
   </si>
   <si>
@@ -1197,9 +1200,6 @@
   </si>
   <si>
     <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -2597,6 +2597,9 @@
     <t>Bundle.entry:Medikationsplan.request.method</t>
   </si>
   <si>
+    <t>PUT</t>
+  </si>
+  <si>
     <t>Bundle.entry:Medikationsplan.request.url</t>
   </si>
   <si>
@@ -2711,6 +2714,9 @@
   </si>
   <si>
     <t>Bundle.entry:Medikationsplaneintrag.request.method</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetMedikationsplanHTTPCodes</t>
   </si>
   <si>
     <t>Bundle.entry:Medikationsplaneintrag.request.url</t>
@@ -3124,7 +3130,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="144.1953125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.65234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3616,7 +3622,7 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
@@ -3844,7 +3850,7 @@
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>21</v>
@@ -5309,14 +5315,14 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -5331,17 +5337,13 @@
         <v>157</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -5407,7 +5409,7 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
@@ -5418,10 +5420,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5432,7 +5434,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -5447,10 +5449,10 @@
         <v>21</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5501,7 +5503,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -5530,10 +5532,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5559,13 +5561,13 @@
         <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5615,7 +5617,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -5644,10 +5646,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5670,13 +5672,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5727,7 +5729,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5756,10 +5758,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5785,10 +5787,10 @@
         <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5839,7 +5841,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5848,7 +5850,7 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
@@ -5868,10 +5870,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5980,10 +5982,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6094,10 +6096,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6210,10 +6212,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6239,13 +6241,13 @@
         <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -6274,10 +6276,10 @@
         <v>127</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -6295,7 +6297,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -6324,10 +6326,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6350,16 +6352,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6409,7 +6411,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -6438,10 +6440,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6467,10 +6469,10 @@
         <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6521,7 +6523,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -6530,7 +6532,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -6550,10 +6552,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6662,10 +6664,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6776,10 +6778,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6892,10 +6894,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6921,10 +6923,10 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6954,10 +6956,10 @@
         <v>127</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -6975,7 +6977,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -7004,10 +7006,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7033,13 +7035,13 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -7089,7 +7091,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -7118,10 +7120,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7147,10 +7149,10 @@
         <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7201,7 +7203,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -7230,10 +7232,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7259,10 +7261,10 @@
         <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7313,7 +7315,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -7342,10 +7344,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7371,10 +7373,10 @@
         <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7425,7 +7427,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -7454,10 +7456,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7483,10 +7485,10 @@
         <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7537,7 +7539,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -7566,10 +7568,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7595,10 +7597,10 @@
         <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7649,7 +7651,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7658,7 +7660,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -7678,10 +7680,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7790,10 +7792,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7904,10 +7906,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8020,10 +8022,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8049,10 +8051,10 @@
         <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -8103,7 +8105,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -8132,10 +8134,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8161,10 +8163,10 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8215,7 +8217,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -8244,10 +8246,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8273,13 +8275,13 @@
         <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8329,7 +8331,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -8358,10 +8360,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8387,13 +8389,13 @@
         <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8443,7 +8445,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -8472,10 +8474,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8498,16 +8500,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8557,7 +8559,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8584,15 +8586,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>21</v>
@@ -8605,7 +8607,7 @@
         <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -8700,7 +8702,7 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>181</v>
@@ -8812,7 +8814,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>182</v>
@@ -8926,7 +8928,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>183</v>
@@ -9042,10 +9044,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9056,7 +9058,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -9068,13 +9070,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9125,7 +9127,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -9152,12 +9154,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9165,13 +9167,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
@@ -9183,13 +9185,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9239,7 +9241,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -9266,16 +9268,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9285,7 +9287,7 @@
         <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
@@ -9294,13 +9296,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9351,7 +9353,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -9369,7 +9371,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -9380,10 +9382,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9409,7 +9411,7 @@
         <v>89</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>91</v>
@@ -9494,10 +9496,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9606,10 +9608,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9718,10 +9720,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9791,16 +9793,16 @@
         <v>21</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>161</v>
@@ -9832,10 +9834,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9861,13 +9863,13 @@
         <v>89</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9917,7 +9919,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9946,10 +9948,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9975,13 +9977,13 @@
         <v>132</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10031,7 +10033,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -10060,10 +10062,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10089,13 +10091,13 @@
         <v>101</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10145,7 +10147,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -10174,10 +10176,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10200,16 +10202,16 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10259,7 +10261,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -10288,10 +10290,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10314,16 +10316,16 @@
         <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10349,13 +10351,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -10373,7 +10375,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10402,10 +10404,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10428,16 +10430,16 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10463,13 +10465,13 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -10487,7 +10489,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10516,10 +10518,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10545,7 +10547,7 @@
         <v>101</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>336</v>
+        <v>102</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>103</v>
@@ -10630,10 +10632,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10744,14 +10746,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10770,16 +10772,16 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10829,7 +10831,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10847,7 +10849,7 @@
         <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>21</v>
@@ -10858,10 +10860,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10970,10 +10972,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11043,16 +11045,16 @@
         <v>21</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>161</v>
@@ -11084,10 +11086,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11113,10 +11115,10 @@
         <v>107</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11146,10 +11148,10 @@
         <v>127</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -11167,7 +11169,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>87</v>
@@ -11196,10 +11198,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11222,16 +11224,16 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11281,7 +11283,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>87</v>
@@ -11293,7 +11295,7 @@
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
@@ -11310,14 +11312,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11336,16 +11338,16 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11395,7 +11397,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11424,10 +11426,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11453,10 +11455,10 @@
         <v>157</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>377</v>
+        <v>185</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11495,14 +11497,14 @@
         <v>21</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC74" s="2"/>
       <c r="AD74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>378</v>
@@ -11537,7 +11539,7 @@
         <v>379</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>380</v>
@@ -11789,10 +11791,10 @@
         <v>157</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>377</v>
+        <v>185</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11831,16 +11833,16 @@
         <v>21</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>161</v>
@@ -12130,7 +12132,7 @@
         <v>404</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>377</v>
+        <v>185</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12729,7 +12731,7 @@
         <v>21</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Y85" t="s" s="2">
         <v>449</v>
@@ -12967,16 +12969,16 @@
         <v>21</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>161</v>
@@ -13034,7 +13036,7 @@
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>460</v>
@@ -13309,16 +13311,16 @@
         <v>21</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>161</v>
@@ -14341,16 +14343,16 @@
         <v>21</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>161</v>
@@ -14557,7 +14559,7 @@
         <v>21</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y101" t="s" s="2">
         <v>550</v>
@@ -14909,16 +14911,16 @@
         <v>21</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>161</v>
@@ -15129,7 +15131,7 @@
         <v>21</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y106" t="s" s="2">
         <v>579</v>
@@ -16281,16 +16283,16 @@
         <v>21</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF116" t="s" s="2">
         <v>161</v>
@@ -16497,7 +16499,7 @@
         <v>21</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y118" t="s" s="2">
         <v>550</v>
@@ -16849,16 +16851,16 @@
         <v>21</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF121" t="s" s="2">
         <v>161</v>
@@ -17069,7 +17071,7 @@
         <v>21</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y123" t="s" s="2">
         <v>579</v>
@@ -18675,16 +18677,16 @@
         <v>21</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF137" t="s" s="2">
         <v>161</v>
@@ -18742,7 +18744,7 @@
         <v>88</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L138" t="s" s="2">
         <v>460</v>
@@ -19017,16 +19019,16 @@
         <v>21</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC140" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF140" t="s" s="2">
         <v>161</v>
@@ -20233,10 +20235,10 @@
         <v>157</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>377</v>
+        <v>185</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -20275,16 +20277,16 @@
         <v>21</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD151" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF151" t="s" s="2">
         <v>161</v>
@@ -20573,10 +20575,10 @@
         <v>157</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>377</v>
+        <v>185</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -20615,16 +20617,16 @@
         <v>21</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF154" t="s" s="2">
         <v>161</v>
@@ -21057,7 +21059,7 @@
         <v>21</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y158" t="s" s="2">
         <v>550</v>
@@ -21637,16 +21639,16 @@
         <v>21</v>
       </c>
       <c r="AB163" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC163" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE163" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF163" t="s" s="2">
         <v>161</v>
@@ -21704,7 +21706,7 @@
         <v>88</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L164" t="s" s="2">
         <v>460</v>
@@ -21979,16 +21981,16 @@
         <v>21</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AF166" t="s" s="2">
         <v>161</v>
@@ -22713,7 +22715,7 @@
         <v>825</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22739,10 +22741,10 @@
         <v>145</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -22793,7 +22795,7 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -22802,7 +22804,7 @@
         <v>87</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AJ173" t="s" s="2">
         <v>99</v>
@@ -22825,7 +22827,7 @@
         <v>826</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22937,7 +22939,7 @@
         <v>827</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23051,7 +23053,7 @@
         <v>828</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23167,7 +23169,7 @@
         <v>829</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23193,13 +23195,13 @@
         <v>107</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23228,10 +23230,10 @@
         <v>127</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>21</v>
@@ -23249,7 +23251,7 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>78</v>
@@ -23281,7 +23283,7 @@
         <v>830</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23304,16 +23306,16 @@
         <v>88</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23363,7 +23365,7 @@
         <v>21</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>78</v>
@@ -23390,12 +23392,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
         <v>831</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23403,13 +23405,13 @@
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G179" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>21</v>
@@ -23421,10 +23423,10 @@
         <v>145</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -23475,7 +23477,7 @@
         <v>21</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>78</v>
@@ -23484,7 +23486,7 @@
         <v>87</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>99</v>
@@ -23507,7 +23509,7 @@
         <v>832</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23619,7 +23621,7 @@
         <v>833</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23733,18 +23735,18 @@
         <v>834</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>21</v>
@@ -23759,17 +23761,13 @@
         <v>157</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N182" s="2"/>
+      <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
         <v>21</v>
       </c>
@@ -23835,7 +23833,7 @@
         <v>21</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM182" t="s" s="2">
         <v>21</v>
@@ -23844,12 +23842,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" hidden="true">
+    <row r="183">
       <c r="A183" t="s" s="2">
         <v>835</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23863,7 +23861,7 @@
         <v>87</v>
       </c>
       <c r="H183" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I183" t="s" s="2">
         <v>21</v>
@@ -23875,10 +23873,10 @@
         <v>107</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -23890,7 +23888,7 @@
         <v>21</v>
       </c>
       <c r="S183" t="s" s="2">
-        <v>21</v>
+        <v>836</v>
       </c>
       <c r="T183" t="s" s="2">
         <v>21</v>
@@ -23908,10 +23906,10 @@
         <v>127</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>21</v>
@@ -23929,7 +23927,7 @@
         <v>21</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>87</v>
@@ -23956,12 +23954,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" hidden="true">
+    <row r="184">
       <c r="A184" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23975,7 +23973,7 @@
         <v>87</v>
       </c>
       <c r="H184" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I184" t="s" s="2">
         <v>21</v>
@@ -23987,13 +23985,13 @@
         <v>101</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -24043,7 +24041,7 @@
         <v>21</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>87</v>
@@ -24072,10 +24070,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24101,10 +24099,10 @@
         <v>150</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -24155,7 +24153,7 @@
         <v>21</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>78</v>
@@ -24184,10 +24182,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24213,10 +24211,10 @@
         <v>132</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -24267,7 +24265,7 @@
         <v>21</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>78</v>
@@ -24296,10 +24294,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24325,10 +24323,10 @@
         <v>150</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -24379,7 +24377,7 @@
         <v>21</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>78</v>
@@ -24408,10 +24406,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24437,10 +24435,10 @@
         <v>150</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
@@ -24491,7 +24489,7 @@
         <v>21</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>78</v>
@@ -24520,10 +24518,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24549,10 +24547,10 @@
         <v>145</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -24603,7 +24601,7 @@
         <v>21</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>78</v>
@@ -24612,7 +24610,7 @@
         <v>87</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>99</v>
@@ -24632,10 +24630,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -24744,10 +24742,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -24858,10 +24856,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -24974,10 +24972,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25003,10 +25001,10 @@
         <v>150</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -25057,7 +25055,7 @@
         <v>21</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>87</v>
@@ -25086,10 +25084,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25115,10 +25113,10 @@
         <v>101</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -25169,7 +25167,7 @@
         <v>21</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>78</v>
@@ -25198,10 +25196,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -25227,13 +25225,13 @@
         <v>150</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -25283,7 +25281,7 @@
         <v>21</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>78</v>
@@ -25312,10 +25310,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -25341,13 +25339,13 @@
         <v>132</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -25397,7 +25395,7 @@
         <v>21</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>78</v>
@@ -25426,10 +25424,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25452,16 +25450,16 @@
         <v>88</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -25511,7 +25509,7 @@
         <v>21</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>78</v>
@@ -25538,15 +25536,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="198" hidden="true">
+    <row r="198">
       <c r="A198" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D198" t="s" s="2">
         <v>21</v>
@@ -25559,7 +25557,7 @@
         <v>79</v>
       </c>
       <c r="H198" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I198" t="s" s="2">
         <v>21</v>
@@ -25654,7 +25652,7 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>181</v>
@@ -25766,7 +25764,7 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>182</v>
@@ -25880,7 +25878,7 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>183</v>
@@ -25996,10 +25994,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26010,7 +26008,7 @@
         <v>78</v>
       </c>
       <c r="G202" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H202" t="s" s="2">
         <v>21</v>
@@ -26022,13 +26020,13 @@
         <v>88</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -26079,7 +26077,7 @@
         <v>21</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>78</v>
@@ -26106,12 +26104,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="203" hidden="true">
+    <row r="203">
       <c r="A203" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26119,13 +26117,13 @@
       </c>
       <c r="E203" s="2"/>
       <c r="F203" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G203" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H203" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I203" t="s" s="2">
         <v>21</v>
@@ -26137,13 +26135,13 @@
         <v>101</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
@@ -26193,7 +26191,7 @@
         <v>21</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>78</v>
@@ -26220,16 +26218,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" hidden="true">
+    <row r="204">
       <c r="A204" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
@@ -26239,7 +26237,7 @@
         <v>87</v>
       </c>
       <c r="H204" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I204" t="s" s="2">
         <v>21</v>
@@ -26248,13 +26246,13 @@
         <v>21</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -26305,7 +26303,7 @@
         <v>21</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>78</v>
@@ -26323,7 +26321,7 @@
         <v>21</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AM204" t="s" s="2">
         <v>21</v>
@@ -26334,10 +26332,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -26363,10 +26361,10 @@
         <v>145</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -26417,7 +26415,7 @@
         <v>21</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>78</v>
@@ -26426,7 +26424,7 @@
         <v>87</v>
       </c>
       <c r="AI205" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AJ205" t="s" s="2">
         <v>99</v>
@@ -26446,10 +26444,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -26558,10 +26556,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -26672,10 +26670,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -26788,10 +26786,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -26817,13 +26815,13 @@
         <v>107</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
@@ -26852,10 +26850,10 @@
         <v>127</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>21</v>
@@ -26873,7 +26871,7 @@
         <v>21</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>78</v>
@@ -26902,10 +26900,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -26928,16 +26926,16 @@
         <v>88</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -26987,7 +26985,7 @@
         <v>21</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>78</v>
@@ -27014,12 +27012,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="211" hidden="true">
+    <row r="211">
       <c r="A211" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27027,13 +27025,13 @@
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G211" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H211" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I211" t="s" s="2">
         <v>21</v>
@@ -27045,10 +27043,10 @@
         <v>145</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -27099,7 +27097,7 @@
         <v>21</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>78</v>
@@ -27108,7 +27106,7 @@
         <v>87</v>
       </c>
       <c r="AI211" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AJ211" t="s" s="2">
         <v>99</v>
@@ -27128,10 +27126,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -27240,10 +27238,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -27354,21 +27352,21 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H214" t="s" s="2">
         <v>21</v>
@@ -27383,17 +27381,13 @@
         <v>157</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N214" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O214" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N214" s="2"/>
+      <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>21</v>
       </c>
@@ -27459,7 +27453,7 @@
         <v>21</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM214" t="s" s="2">
         <v>21</v>
@@ -27468,12 +27462,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="215" hidden="true">
+    <row r="215">
       <c r="A215" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -27487,7 +27481,7 @@
         <v>87</v>
       </c>
       <c r="H215" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I215" t="s" s="2">
         <v>21</v>
@@ -27499,10 +27493,10 @@
         <v>107</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
@@ -27531,11 +27525,9 @@
       <c r="X215" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="Y215" t="s" s="2">
-        <v>223</v>
-      </c>
+      <c r="Y215" s="2"/>
       <c r="Z215" t="s" s="2">
-        <v>224</v>
+        <v>875</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>21</v>
@@ -27553,7 +27545,7 @@
         <v>21</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>87</v>
@@ -27580,12 +27572,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" hidden="true">
+    <row r="216">
       <c r="A216" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -27599,7 +27591,7 @@
         <v>87</v>
       </c>
       <c r="H216" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I216" t="s" s="2">
         <v>21</v>
@@ -27611,13 +27603,13 @@
         <v>101</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
@@ -27667,7 +27659,7 @@
         <v>21</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>87</v>
@@ -27696,10 +27688,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -27725,10 +27717,10 @@
         <v>150</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
@@ -27779,7 +27771,7 @@
         <v>21</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>78</v>
@@ -27808,10 +27800,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -27837,10 +27829,10 @@
         <v>132</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -27891,7 +27883,7 @@
         <v>21</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>78</v>
@@ -27920,10 +27912,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -27949,10 +27941,10 @@
         <v>150</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
@@ -28003,7 +27995,7 @@
         <v>21</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>78</v>
@@ -28032,10 +28024,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -28061,10 +28053,10 @@
         <v>150</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
@@ -28115,7 +28107,7 @@
         <v>21</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>78</v>
@@ -28144,10 +28136,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -28173,10 +28165,10 @@
         <v>145</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" s="2"/>
@@ -28227,7 +28219,7 @@
         <v>21</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>78</v>
@@ -28236,7 +28228,7 @@
         <v>87</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AJ221" t="s" s="2">
         <v>99</v>
@@ -28256,10 +28248,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -28368,10 +28360,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -28482,10 +28474,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -28598,10 +28590,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -28627,10 +28619,10 @@
         <v>150</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -28681,7 +28673,7 @@
         <v>21</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>87</v>
@@ -28710,10 +28702,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -28739,10 +28731,10 @@
         <v>101</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -28793,7 +28785,7 @@
         <v>21</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>78</v>
@@ -28822,10 +28814,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -28851,13 +28843,13 @@
         <v>150</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
@@ -28907,7 +28899,7 @@
         <v>21</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>78</v>
@@ -28936,10 +28928,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -28965,13 +28957,13 @@
         <v>132</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
@@ -29021,7 +29013,7 @@
         <v>21</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>78</v>
@@ -29050,10 +29042,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -29076,16 +29068,16 @@
         <v>88</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O229" s="2"/>
       <c r="P229" t="s" s="2">
@@ -29135,7 +29127,7 @@
         <v>21</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>78</v>
@@ -29164,10 +29156,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -29190,19 +29182,19 @@
         <v>88</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="O230" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>21</v>
@@ -29251,7 +29243,7 @@
         <v>21</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>78</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1650,7 +1650,7 @@
     <t>Bundle.entry.resource.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-patient)
 </t>
   </si>
   <si>
@@ -2021,7 +2021,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung)
 </t>
   </si>
   <si>
@@ -3115,7 +3115,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="201.5546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="205.203125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8271" uniqueCount="896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8271" uniqueCount="898">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1313,7 +1313,7 @@
     <t>Bundle.entry.resource.status</t>
   </si>
   <si>
-    <t>Status des Medikationsplans. Fixer Wert: current</t>
+    <t>Status des Medikationsplans. Fixer Wert: current.</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -1407,7 +1407,7 @@
 </t>
   </si>
   <si>
-    <t>Code der den Medikationsplan identifiziert</t>
+    <t>Code, der den Medikationsplan identifiziert.</t>
   </si>
   <si>
     <t>This code defines the purpose of the list - why it was created.</t>
@@ -1623,7 +1623,7 @@
     <t>Bundle.entry.resource.code.text</t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
+    <t>Plain text representation of the concept</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -1776,6 +1776,9 @@
     <t>Bundle.entry.resource.subject.identifier.use</t>
   </si>
   <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
     <t>The purpose of this identifier.</t>
   </si>
   <si>
@@ -2136,6 +2139,9 @@
     <t>Bundle.entry.resource.orderedBy</t>
   </si>
   <si>
+    <t>What order the list has</t>
+  </si>
+  <si>
     <t>What order applies to the items in the list.</t>
   </si>
   <si>
@@ -2167,7 +2173,7 @@
 </t>
   </si>
   <si>
-    <t>Fachliche Begründung: Auf dieser Ebene keine Freitext-Anmerkungen im Medikationsplan. Freitext ist in den jeweiligen MedicationRequests(Planeinträgen möglich)</t>
+    <t>Fachliche Begründung: Auf dieser Ebene existieren keine Freitext-Anmerkungen im Medikationsplan. Freitext ist in den jeweiligen MedicationRequests (Planeinträgen möglich).</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>
@@ -2228,7 +2234,7 @@
     <t>Bundle.entry.resource.entry.flag</t>
   </si>
   <si>
-    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: [New | Unchanged | Changed | Removed] Bedeutung: New: Neuer Planeintrag wird hinzugefügt | Unchanged: Bestehender Planeintrag wird beibehalten und zur Kenntnis genommen | Changed: Bestehender Planeintrag wird geändert | Removed: Bestehender Planeintrag wird entfernt</t>
+    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: [new | unchanged | changed | removed]. Bedeutung: new: Neuer Planeintrag wird hinzugefügt | unchanged: Bestehender Planeintrag wird beibehalten und zur Kenntnis genommen | changed: Bestehender Planeintrag wird geändert | removed: Bestehender Planeintrag wird entfernt</t>
   </si>
   <si>
     <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
@@ -2349,7 +2355,7 @@
     <t>Bundle.entry.resource.entry.date</t>
   </si>
   <si>
-    <t>Fachliche Begründung: Das Datum der initialen Aufnahme eines Eintrags wird nicht auf Ebene der Liste dokumentiert. Datumsinformationen werden im referenzierten Medikationsplaneintrag dokumentiert.</t>
+    <t>Fachliche Begründung: Das Datum der initialen Aufnahme eines Eintrags wird nicht auf Ebene der Liste, sondern im referenzierten Medikationsplaneintrag dokumentiert.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -2477,7 +2483,7 @@
     <t>Bundle.entry.resource.emptyReason</t>
   </si>
   <si>
-    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown ] Bedeutung: notstarted: Intitalzustand - noch nie befüllt; nilknown: Der Plan wurde vom GDA explizit als leer dokumentiert oder alle Einträge wurden abgesetzt, storniert oder gelöscht.</t>
+    <t>Begründung, welshalb der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown ] Bedeutung: notstarted: Intitalzustand - noch nie befüllt; nilknown: Der Plan wurde vom GDA explizit als leer dokumentiert oder alle Einträge wurden abgesetzt, storniert oder gelöscht.</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>
@@ -14981,16 +14987,16 @@
         <v>107</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>517</v>
+        <v>566</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>21</v>
@@ -15018,10 +15024,10 @@
         <v>127</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>21</v>
@@ -15039,7 +15045,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15057,7 +15063,7 @@
         <v>84</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>21</v>
@@ -15068,10 +15074,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15097,16 +15103,16 @@
         <v>444</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>21</v>
@@ -15134,10 +15140,10 @@
         <v>323</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>21</v>
@@ -15155,7 +15161,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15170,10 +15176,10 @@
         <v>99</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>21</v>
@@ -15184,10 +15190,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15213,16 +15219,16 @@
         <v>101</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
@@ -15235,7 +15241,7 @@
         <v>21</v>
       </c>
       <c r="T107" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="U107" t="s" s="2">
         <v>21</v>
@@ -15271,7 +15277,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15286,10 +15292,10 @@
         <v>99</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>21</v>
@@ -15300,10 +15306,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15329,13 +15335,13 @@
         <v>150</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15349,7 +15355,7 @@
         <v>21</v>
       </c>
       <c r="T108" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="U108" t="s" s="2">
         <v>21</v>
@@ -15385,7 +15391,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15400,10 +15406,10 @@
         <v>99</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>21</v>
@@ -15414,10 +15420,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15440,13 +15446,13 @@
         <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15497,7 +15503,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15512,10 +15518,10 @@
         <v>99</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>21</v>
@@ -15526,10 +15532,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15552,16 +15558,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15611,7 +15617,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15626,10 +15632,10 @@
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>21</v>
@@ -15640,10 +15646,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15669,13 +15675,13 @@
         <v>150</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15725,7 +15731,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15754,10 +15760,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15780,13 +15786,13 @@
         <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15837,7 +15843,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15855,21 +15861,21 @@
         <v>21</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15892,19 +15898,19 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
@@ -15953,7 +15959,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15971,25 +15977,25 @@
         <v>21</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -16008,19 +16014,19 @@
         <v>88</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>21</v>
@@ -16069,7 +16075,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16087,21 +16093,21 @@
         <v>21</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16210,10 +16216,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16324,10 +16330,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16438,10 +16444,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16552,10 +16558,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16666,10 +16672,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16778,10 +16784,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16892,10 +16898,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16921,16 +16927,16 @@
         <v>107</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>517</v>
+        <v>566</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>21</v>
@@ -16958,10 +16964,10 @@
         <v>127</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>21</v>
@@ -16979,7 +16985,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16997,7 +17003,7 @@
         <v>84</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>21</v>
@@ -17008,10 +17014,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17037,16 +17043,16 @@
         <v>444</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>21</v>
@@ -17074,10 +17080,10 @@
         <v>323</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>21</v>
@@ -17095,7 +17101,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17110,10 +17116,10 @@
         <v>99</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>21</v>
@@ -17124,10 +17130,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17153,16 +17159,16 @@
         <v>101</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>21</v>
@@ -17175,7 +17181,7 @@
         <v>21</v>
       </c>
       <c r="T124" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="U124" t="s" s="2">
         <v>21</v>
@@ -17211,7 +17217,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17226,10 +17232,10 @@
         <v>99</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>21</v>
@@ -17240,10 +17246,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17269,13 +17275,13 @@
         <v>150</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17289,7 +17295,7 @@
         <v>21</v>
       </c>
       <c r="T125" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="U125" t="s" s="2">
         <v>21</v>
@@ -17325,7 +17331,7 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17340,10 +17346,10 @@
         <v>99</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>21</v>
@@ -17354,10 +17360,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17380,13 +17386,13 @@
         <v>88</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17437,7 +17443,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -17452,10 +17458,10 @@
         <v>99</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>21</v>
@@ -17466,10 +17472,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17492,16 +17498,16 @@
         <v>88</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17551,7 +17557,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17566,10 +17572,10 @@
         <v>99</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>21</v>
@@ -17580,10 +17586,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17609,13 +17615,13 @@
         <v>150</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17665,7 +17671,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17694,10 +17700,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17723,16 +17729,16 @@
         <v>444</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>517</v>
+        <v>685</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>21</v>
@@ -17760,10 +17766,10 @@
         <v>111</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>21</v>
@@ -17781,7 +17787,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17799,7 +17805,7 @@
         <v>21</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>21</v>
@@ -17810,10 +17816,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17836,13 +17842,13 @@
         <v>21</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17893,7 +17899,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17911,7 +17917,7 @@
         <v>21</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>21</v>
@@ -17922,10 +17928,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17951,13 +17957,13 @@
         <v>145</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18007,7 +18013,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -18016,7 +18022,7 @@
         <v>79</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>99</v>
@@ -18025,7 +18031,7 @@
         <v>21</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>21</v>
@@ -18036,10 +18042,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18148,10 +18154,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18262,10 +18268,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18378,10 +18384,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18407,16 +18413,16 @@
         <v>444</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>21</v>
@@ -18445,7 +18451,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>21</v>
@@ -18463,7 +18469,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18492,10 +18498,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18604,10 +18610,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18718,10 +18724,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18834,10 +18840,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18946,10 +18952,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19060,10 +19066,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19176,10 +19182,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19290,10 +19296,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19404,10 +19410,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19518,10 +19524,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19634,10 +19640,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19750,10 +19756,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19779,22 +19785,22 @@
         <v>398</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q147" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="R147" t="s" s="2">
         <v>21</v>
@@ -19839,7 +19845,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19848,7 +19854,7 @@
         <v>87</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>99</v>
@@ -19857,7 +19863,7 @@
         <v>21</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>21</v>
@@ -19868,10 +19874,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19894,17 +19900,17 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>21</v>
@@ -19953,7 +19959,7 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19971,7 +19977,7 @@
         <v>21</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>21</v>
@@ -19982,10 +19988,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20008,13 +20014,13 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20065,7 +20071,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>87</v>
@@ -20083,7 +20089,7 @@
         <v>21</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>21</v>
@@ -20094,10 +20100,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20206,10 +20212,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20318,13 +20324,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>21</v>
@@ -20346,16 +20352,16 @@
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -20434,10 +20440,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20546,10 +20552,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20658,10 +20664,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20701,7 +20707,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>21</v>
@@ -20772,10 +20778,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20816,7 +20822,7 @@
         <v>21</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>21</v>
@@ -20884,10 +20890,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20998,10 +21004,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21112,10 +21118,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21226,10 +21232,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21255,13 +21261,13 @@
         <v>150</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -21311,7 +21317,7 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -21340,10 +21346,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21369,16 +21375,16 @@
         <v>444</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>21</v>
@@ -21407,7 +21413,7 @@
       </c>
       <c r="Y161" s="2"/>
       <c r="Z161" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>21</v>
@@ -21425,7 +21431,7 @@
         <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -21434,7 +21440,7 @@
         <v>87</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>99</v>
@@ -21443,7 +21449,7 @@
         <v>21</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>21</v>
@@ -21454,10 +21460,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21566,10 +21572,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21680,10 +21686,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21796,10 +21802,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21908,10 +21914,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22022,10 +22028,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22138,10 +22144,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22252,10 +22258,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22366,10 +22372,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22480,10 +22486,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22596,10 +22602,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22712,7 +22718,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>197</v>
@@ -22824,7 +22830,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>201</v>
@@ -22936,7 +22942,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>202</v>
@@ -23050,7 +23056,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>203</v>
@@ -23166,7 +23172,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>204</v>
@@ -23280,7 +23286,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>210</v>
@@ -23394,7 +23400,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>215</v>
@@ -23506,7 +23512,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>219</v>
@@ -23618,7 +23624,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>220</v>
@@ -23732,7 +23738,7 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>221</v>
@@ -23844,7 +23850,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>222</v>
@@ -23888,7 +23894,7 @@
         <v>21</v>
       </c>
       <c r="S183" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="T183" t="s" s="2">
         <v>21</v>
@@ -23956,7 +23962,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>227</v>
@@ -24070,7 +24076,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>231</v>
@@ -24182,7 +24188,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>234</v>
@@ -24294,7 +24300,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>236</v>
@@ -24406,7 +24412,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>239</v>
@@ -24518,7 +24524,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>242</v>
@@ -24630,7 +24636,7 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>246</v>
@@ -24742,7 +24748,7 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>247</v>
@@ -24856,7 +24862,7 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>248</v>
@@ -24972,7 +24978,7 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>249</v>
@@ -25084,7 +25090,7 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>252</v>
@@ -25196,7 +25202,7 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>255</v>
@@ -25310,7 +25316,7 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>259</v>
@@ -25424,7 +25430,7 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>263</v>
@@ -25538,13 +25544,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D198" t="s" s="2">
         <v>21</v>
@@ -25652,7 +25658,7 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>181</v>
@@ -25764,7 +25770,7 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>182</v>
@@ -25878,7 +25884,7 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>183</v>
@@ -25994,7 +26000,7 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>186</v>
@@ -26106,7 +26112,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>189</v>
@@ -26220,14 +26226,14 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
@@ -26246,13 +26252,13 @@
         <v>21</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -26321,7 +26327,7 @@
         <v>21</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="AM204" t="s" s="2">
         <v>21</v>
@@ -26332,7 +26338,7 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>197</v>
@@ -26444,7 +26450,7 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>201</v>
@@ -26556,7 +26562,7 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>202</v>
@@ -26670,7 +26676,7 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>203</v>
@@ -26786,7 +26792,7 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>204</v>
@@ -26900,7 +26906,7 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>210</v>
@@ -27014,7 +27020,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>215</v>
@@ -27126,7 +27132,7 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>219</v>
@@ -27238,7 +27244,7 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>220</v>
@@ -27352,7 +27358,7 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>221</v>
@@ -27464,7 +27470,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>222</v>
@@ -27527,7 +27533,7 @@
       </c>
       <c r="Y215" s="2"/>
       <c r="Z215" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>21</v>
@@ -27574,7 +27580,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>227</v>
@@ -27688,7 +27694,7 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>231</v>
@@ -27800,7 +27806,7 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>234</v>
@@ -27912,7 +27918,7 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>236</v>
@@ -28024,7 +28030,7 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>239</v>
@@ -28136,7 +28142,7 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>242</v>
@@ -28248,7 +28254,7 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>246</v>
@@ -28360,7 +28366,7 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>247</v>
@@ -28474,7 +28480,7 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>248</v>
@@ -28590,7 +28596,7 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>249</v>
@@ -28702,7 +28708,7 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>252</v>
@@ -28814,7 +28820,7 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>255</v>
@@ -28928,7 +28934,7 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>259</v>
@@ -29042,7 +29048,7 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>263</v>
@@ -29156,10 +29162,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -29182,19 +29188,19 @@
         <v>88</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="O230" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>21</v>
@@ -29243,7 +29249,7 @@
         <v>21</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>78</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2680,7 +2680,7 @@
 </t>
   </si>
   <si>
-    <t>Planeintrag</t>
+    <t>Ordering of medication for patient or group</t>
   </si>
   <si>
     <t>An order or request for both supply of the medication and the instructions for administration of the medication to a patient. The resource is called "MedicationRequest" rather than "MedicationPrescription" or "MedicationOrder" to generalize the use across inpatient and outpatient settings, including care plans, etc., and to harmonize with workflow patterns.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -20229,7 +20229,7 @@
         <v>79</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>21</v>
@@ -20322,7 +20322,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
         <v>772</v>
       </c>
@@ -20343,7 +20343,7 @@
         <v>87</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>21</v>
@@ -20776,7 +20776,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
         <v>785</v>
       </c>
@@ -20795,7 +20795,7 @@
         <v>87</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8271" uniqueCount="898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8267" uniqueCount="898">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8941,14 +8941,14 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -8963,17 +8963,13 @@
         <v>157</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -9039,7 +9035,7 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
@@ -25891,14 +25887,14 @@
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E201" s="2"/>
       <c r="F201" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H201" t="s" s="2">
         <v>21</v>
@@ -25913,17 +25909,13 @@
         <v>157</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O201" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N201" s="2"/>
+      <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
         <v>21</v>
       </c>
@@ -25989,7 +25981,7 @@
         <v>21</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8126" uniqueCount="889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8124" uniqueCount="889">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -11418,7 +11418,7 @@
         <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
@@ -17794,14 +17794,14 @@
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>21</v>
@@ -17816,17 +17816,13 @@
         <v>157</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>165</v>
+        <v>387</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>21</v>
       </c>
@@ -17892,7 +17888,7 @@
         <v>21</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2198,7 +2198,7 @@
     <t>This field is present to support various clinical uses of lists, such as a discharge summary medication list, where flags specify whether the medication was added, modified, or deleted from the list.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListEntryFlagVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-listentryflag-vs</t>
   </si>
   <si>
     <t>List.entry.flag</t>
@@ -2468,7 +2468,7 @@
     <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListEmptyReasonVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-listemptyreason-vs</t>
   </si>
   <si>
     <t>List.emptyReason</t>
@@ -2695,7 +2695,7 @@
     <t>Bundle.entry:Medikationsplaneintrag.request.method</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetMedikationsplanHTTPCodes</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-medikationsplan-http-codes-vs</t>
   </si>
   <si>
     <t>Bundle.entry:Medikationsplaneintrag.request.url</t>
@@ -3109,7 +3109,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="144.1953125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.65234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="76.0" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
